--- a/note ゼロイチ実証ログ.xlsx
+++ b/note ゼロイチ実証ログ.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,18 +48,13 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -122,45 +117,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,13 +525,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -546,284 +544,364 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ このシートは募集文の下書きです。実際の募集時にコピーして使用してください。</t>
+          <t>※ 募集文の下書きです。実際の募集時にコピーして使用してください。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>段階投入の設計</t>
+          <t>このモニターの位置づけ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>・目的は「成功させること」ではなく、手順を改善して再現性を高めること（PDCAのC→A）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>・したがって達成率そのものは評価対象にしない。達成しなかった場合の記録が最も価値が高い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>・第1陣で穴を潰し、改善後の第2陣の結果を実証数字として扱う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>段階投入の設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>目的・扱い</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
+    <row r="12" ht="34" customHeight="1">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>0. 自分</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>1名（本人）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>新規0フォロワーアカウントで完走し、手順を体系化する。ここが終わるまでモニターは開始しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>新規0フォロワーアカウントで完走し、手順を体系化する。あわせて自分の作業時間を計測し、参加条件の「1日の作業時間」をここで確定させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>1. 第1陣</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>3名</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>教材の穴出しが目的。達成率は実証数字に含めない。募集時に「検証目的である」と明示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>教材の穴出しが目的。達成率は実証数字に含めない。Claude Codeの1週間無料体験を提供できるのはこの枠。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>2. 改善</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>第1陣が詰まった箇所を教材・手順に反映する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>第1陣が詰まった箇所を手順・ツール・レクチャーに反映する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>3. 第2陣</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>7名</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>本番。ここの達成率を実証数字として運営に提示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>改善版で実施。ここの結果を実証数字として運営に提示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>参加条件（すべて満たす方）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>条件</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>なぜこの条件が必要か</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>コンテンツ販売での売上が0円の方（ゼロイチ未達）</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>「ゼロイチを達成させた」という主張の前提。すでに売上がある人が達成しても証拠にならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>noteの新規アカウントを用意できる方（フォロワー0から開始）</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>「フォロワー0から売れる」ことの証明に必須。既存アカウントでは再現性を主張できない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>1日30分以上の作業時間を確保できる方（1週間）</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>「集中できる方」では主観になり測れない。時間で定義することで、そのまま低負荷の証拠になる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Claudeのサブスクを契約できる方</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>AIツールの利用が前提のため。※自分の検証時に無料版で回るか確認し、可能なら条件から外す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>実証ログを毎日提出できる方（Googleフォーム／所要2〜3分）</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>最優先の条件。ログが取れなければ実証そのものが成立しない。</t>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>補足</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>コンテンツ販売での売上が0円の方（ゼロイチ未達）</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>「ゼロイチを達成させた」という主張の前提。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>noteの新規アカウントを用意できる方（フォロワー0から開始）</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>「フォロワー0から売れる」ことの証明に必須。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>1日◯分以上の作業時間を確保できる方（1週間）</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>※ 数値は本人の検証（段階0）の実測値をもとに確定する。それまで空欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Claude Codeのサブスクを契約できる方</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>提供ツールがClaude Code前提のため必須。第1陣3名までは1週間の無料体験を提供。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>初回レクチャー（Claude Code＋ツールの使い方）に参加できる方</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>必須。ここを飛ばすと全員が同じ箇所で詰まるため。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>成果・体験談の公開に同意できる方（実名/ニックネーム/匿名は選択可）</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>事例として使用するため。後から依頼すると断られるので入口で取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>辞退・除外の扱い（募集時に明記）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>・3日以上ログの提出および連絡がない場合は、辞退とみなし実証対象から除外します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>・除外者は達成率の母数から外し、その旨を実証結果に明記します（母数を操作しないため）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>・期間内に売上が発生しなかった場合も、ログは最後まで提出をお願いします（改善材料として最も価値があるため）。</t>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>実証ログを提出できる方（1日1回・約30秒／終了時に1回）</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>改善材料の収集が本モニターの主目的。負担は最小限に設計。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>参加者に約束すること</t>
+          <t>成果・体験談の公開について（募集文に明記）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>・手順書、AIツール、テンプレートの提供</t>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>・本モニターで得られた成果・数値・体験談は、講座および運営への報告に使用します。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>・お申し込みをもって、上記への同意をいただいたものとみなします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>・公開名義は「実名／ニックネーム／匿名」から選べます（完了時アンケートで指定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>提供内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>・初回レクチャー（Claude Code の導入＋ツールの使い方）※必須参加</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>・手順書、AIツール、テンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>・期間中の質問対応（詰まった箇所は必ず解消する）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>・※ 具体的な提供内容・価格・サポート範囲は本人記入</t>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>・第1陣3名まで：Claude Code 1週間無料体験</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>※ 価格・サポート範囲は本人記入</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>辞退・除外の扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>・3日以上ログの提出および連絡がない場合は、辞退とみなし集計対象から除外します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>・除外者は母数から外し、その旨を実証結果に明記します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>・売上が発生しなかった場合も、ログは最後まで提出をお願いします（改善材料として最も価値があるため）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="21">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B39:D39"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -836,15 +914,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F47"/>
+  <dimension ref="B2:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -857,922 +935,838 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ フォームは3つ作成します：A=参加時プロフィール（1回）／B=日次ログ（毎日）／C=完了サマリ（終了時1回）</t>
+          <t>※ フォームは3つ：A=申込時（1回）／B=日次ログ（毎日・約30秒）／C=完了時（1回）。詳細な設問はすべてCに寄せ、Bは負担を最小化しています。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>フォームA｜参加時プロフィール（開始前に1回）</t>
+          <t>フォームA｜申込時（1回・約2分）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>設問</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>回答形式</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>選択肢</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>何の証拠になるか</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="7" t="n">
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>お名前（ニックネーム可）</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>記述</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>識別用</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="7" t="n">
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>第何陣ですか</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>第1陣 / 第2陣</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>陣別集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>開始日</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>経過日数の起点</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>第何陣ですか</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>本業の形態</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>第1陣 / 第2陣</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>陣別の達成率を出すため</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>本業の形態</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>フルタイム勤務 / パート・アルバイト / 専業主婦・主夫 / 自営 / 無職・休職中 / その他</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>「忙しい人でもできた」の裏付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>1日に確保できる作業時間</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>フルタイム勤務 / パート・アルバイト / 専業主婦・主夫 / 自営 / 無職・休職中 / その他</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>「忙しい人でも達成できた」の裏付け</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>1日に確保できる作業時間</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>30分未満 / 30分〜1時間 / 1〜2時間 / 2時間以上</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>低負荷であることの前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>文章を書いた経験</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>30分未満 / 30分〜1時間 / 1〜2時間 / 2時間以上</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>低負荷であることの前提条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>文章を書いた経験</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>ほぼない / SNS投稿程度 / ブログ経験あり / 仕事で日常的に書く</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>「未経験でもできた」の裏付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>これまでのコンテンツ販売の売上</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>ほぼない / SNS投稿程度 / ブログ経験あり / 仕事で日常的に書く</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>「文章未経験でもできた」の裏付け</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>noteの利用経験</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>0円 / 1〜9,999円 / 1万円以上</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>ゼロイチ未達の確認（参加条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>開始時のフォロワー数</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0からの達成であることの証明</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Claude Code / AIツールの使用経験</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>使ったことがない / 読むだけ / 無料記事を書いたことがある</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>開始地点の記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>これまでのコンテンツ販売の売上</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>まったくない / 少し使ったことがある / 日常的に使う</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>レクチャー内容の調整・「初心者でもできた」の裏付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>販売する題材（ネタ）はありますか</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>0円 / 1〜9,999円 / 1万円以上</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>ゼロイチ未達の確認（参加条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>開始時のフォロワー数</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>0からの達成であることの証明</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>AIツールの使用経験</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>まったくない / 少し使ったことがある / 日常的に使う</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>「AI初心者でもできた」の裏付け</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="7" t="n">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>すでに決まっている / 候補はある / まったくない</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>題材ゼロでも到達できるかの検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>販売する題材（ネタ）はありますか</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>すでに決まっている / 候補はある / まったくない</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>題材ゼロの人でも到達できるかの検証</t>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>成果・体験談の公開に同意します</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>チェック</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>同意する（必須）</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>申込＝同意として記録に残す</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>フォームB｜日次ログ（毎日・所要2〜3分）</t>
+          <t>フォームB｜日次ログ（毎日・約30秒）★4問のみ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>設問</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>回答形式</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>選択肢</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>何の証拠になるか</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="7" t="n">
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>お名前（ニックネーム可）</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>（登録者から選択）</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>個人の紐付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>何日目ですか</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>1 / 2 / 3 / 4 / 5 / 6 / 7 / 8日目以降</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>経過日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>今日の作業時間</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>0分（作業なし） / 30分未満 / 30分〜1時間 / 1〜2時間 / 2時間以上</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>総作業時間の集計元</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>今日つまずいたことがあれば（任意・一言でOK）</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>記述（任意）</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>★ 改善の最重要データ。ここだけは鮮度が命なので日次で取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>売上は発生しましたか</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>まだ / 発生した</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>ゼロイチ達成の判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>フォームC｜完了時（1回・約5分）※詳細はすべてここ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>設問</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>回答形式</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>何の証拠になるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>お名前（ニックネーム可）</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>記述</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>個人の紐付け</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="7" t="n">
+      <c r="E29" s="7" t="inlineStr"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>識別用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>経過日数の算出</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="7" t="n">
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>ゼロイチを達成しましたか</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>達成した / 達成できなかった</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>達成率の集計元</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>何日目ですか</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>初売上までの日数</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>数値</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>経過日数</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="7" t="n">
+      <c r="E31" s="7" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>「◯日で達成」の根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>今日の作業時間</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>初売上までの総作業時間（時間）</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>★ 差別化の中核。日次ログと突き合わせて検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>売上金額 / 購入者数</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>記述</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>達成内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>AIで生成した文章の割合（全体を通して）</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>30分未満 / 30分〜1時間 / 1〜2時間 / 2〜3時間 / 3時間以上</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>★ 総作業時間の集計元。「労力が少ない」の唯一の証拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>今日進めた工程（複数選択可）</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>ほぼ全部（90%以上） / 大半（70%程度） / 半分くらい / 一部（30%程度） / ほぼ使わなかった</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>「書けない人でもできる」の裏付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="B35" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>AIの文章に手直しは必要でしたか</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ほぼそのまま使えた / 少し直した / 半分くらい直した / 大幅に直した / 使えず自分で書き直した</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>★ ツールの完成度。改善対象の特定</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="B36" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>手直しした理由（複数選択可）</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>選択(複数)</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>題材決め / 構成作成 / 本文作成 / タイトル・見出し / 価格設定 / 記事公開 / 告知・集客 / その他</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>どの工程に時間がかかるかの特定</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>AIで生成した文章の割合</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>自分の言葉になっていない / 内容が薄い / 事実と違う / 長すぎる・短すぎる / 構成が合わない / 手直しは不要だった</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>プロンプト改善の直接材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>全体を通しての負荷感</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>ほぼ全部（90%以上） / 大半（70%程度） / 半分くらい / 一部（30%程度） / ほぼ使わなかった</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>★ AI活用度。「書けない人でもできる」の裏付け</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="B27" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>AIの文章に手直しは必要でしたか</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>余裕があった / ちょうどよかった / ややきつかった / かなりきつかった</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>「労力が少ない」の主観的裏付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>最もつまずいた工程</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ほぼそのまま使えた / 少し直した / 半分くらい直した / 大幅に直した / 使えず自分で書き直した</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>★ ツールの完成度。手直しが多ければ改善対象</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="B28" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>手直しした理由（複数選択可）</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>選択(複数)</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>自分の言葉になっていない / 内容が薄い / 事実と違う / 長すぎる・短すぎる / 構成が合わない / 手直しは不要だった</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>プロンプト改善の直接材料</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="B29" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>今日つまずいた箇所</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>題材決め / 構成作成 / 本文作成 / 価格設定 / 記事公開 / 告知・集客 / Claude Codeの操作</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>★ 教材・レクチャーの弱点特定</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="B39" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>レクチャー・手順書で分かりにくかった点</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>記述</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>★ 教材・FAQに直結する最重要データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="B30" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>そのつまずきは解決しましたか</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr"/>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>改善材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="B40" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>一番役に立った点</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>記述</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>セールス材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="B41" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>この講座を同じ状況の人に勧めますか（0〜10）</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>0〜10</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>推奨度</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="B42" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>公開時の名義</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>自力で解決 / 教材を見て解決 / 質問して解決 / 未解決のまま</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>教材だけで自走できるかの判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="B31" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>今日の負荷感</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>余裕があった / ちょうどよかった / ややきつかった / かなりきつかった</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>★ 主観的負荷。「労力が少ない」のもう一つの証拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>売上は発生しましたか</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>まだ / 発生した</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>ゼロイチ達成の判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="B33" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>（発生した場合）金額と購入者数</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>実名 / ニックネーム / 匿名</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>公開同意は申込時に取得済み。名義のみ確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="B43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>体験談（自由記述）</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>記述</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>達成内容の記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>フォームC｜完了サマリ（終了時に1回）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>設問</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>回答形式</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>選択肢</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>何の証拠になるか</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="B37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>お名前（ニックネーム可）</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>記述</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>識別用</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="B38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>ゼロイチを達成しましたか</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>達成した / 達成できなかった</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>★ 達成率の集計元</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="B39" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>初売上までの日数</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>★「◯日で達成」の根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>初売上までの総作業時間（時間）</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>★「総作業◯時間」の根拠。日次ログと突き合わせて検証</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="B41" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>売上金額 / 購入者数</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>記述</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>達成内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="B42" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>最もつまずいた工程</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>題材決め / 構成作成 / 本文作成 / 価格設定 / 記事公開 / 告知・集客</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>教材の弱点特定</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="B43" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>教材で分かりにくかった点</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>記述</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>改善材料</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="B44" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>一番役に立った点</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>記述</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>セールス材料</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="B45" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>この講座を同じ状況の人に勧めますか（0〜10）</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>0〜10</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>推奨度。運営提示時の指標</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="B46" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>成果・体験談の公開可否</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>実名で可 / ニックネームで可 / 匿名なら可 / 不可</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>事例利用の許諾</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="B47" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>体験談（自由記述）</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>記述</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr"/>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>お客様の声</t>
         </is>
@@ -1782,8 +1776,8 @@
   <mergeCells count="4">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1795,23 +1789,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N85"/>
+  <dimension ref="B2:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1824,74 +1811,39 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ Googleフォームの回答をここに貼り付けて蓄積します。この表のデータは⑤実証結果集計には直接使いません（集計は④を参照）。</t>
+          <t>※ Googleフォーム（B）の回答をここに貼り付けて蓄積します。E列のつまずきが改善の一次材料です。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>参加者</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>日目</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>作業時間</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>進めた工程</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>AI生成割合</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>手直しの程度</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>手直しの理由</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>つまずいた箇所</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>解決状況</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>負荷感</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>つまずいたこと</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>売上発生</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>金額・購入者数</t>
         </is>
       </c>
     </row>
@@ -1902,13 +1854,6 @@
       <c r="E6" s="13" t="n"/>
       <c r="F6" s="13" t="n"/>
       <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="13" t="n"/>
@@ -1917,13 +1862,6 @@
       <c r="E7" s="13" t="n"/>
       <c r="F7" s="13" t="n"/>
       <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="13" t="n"/>
@@ -1932,13 +1870,6 @@
       <c r="E8" s="13" t="n"/>
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="13" t="n"/>
@@ -1947,13 +1878,6 @@
       <c r="E9" s="13" t="n"/>
       <c r="F9" s="13" t="n"/>
       <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="13" t="n"/>
@@ -1962,13 +1886,6 @@
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="13" t="n"/>
@@ -1977,13 +1894,6 @@
       <c r="E11" s="13" t="n"/>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="n"/>
-      <c r="N11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="13" t="n"/>
@@ -1992,13 +1902,6 @@
       <c r="E12" s="13" t="n"/>
       <c r="F12" s="13" t="n"/>
       <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="13" t="n"/>
-      <c r="N12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="13" t="n"/>
@@ -2007,13 +1910,6 @@
       <c r="E13" s="13" t="n"/>
       <c r="F13" s="13" t="n"/>
       <c r="G13" s="13" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="13" t="n"/>
@@ -2022,13 +1918,6 @@
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="13" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="13" t="n"/>
@@ -2037,13 +1926,6 @@
       <c r="E15" s="13" t="n"/>
       <c r="F15" s="13" t="n"/>
       <c r="G15" s="13" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="13" t="n"/>
-      <c r="N15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="13" t="n"/>
@@ -2052,13 +1934,6 @@
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="13" t="n"/>
@@ -2067,13 +1942,6 @@
       <c r="E17" s="13" t="n"/>
       <c r="F17" s="13" t="n"/>
       <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="13" t="n"/>
@@ -2082,13 +1950,6 @@
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="13" t="n"/>
-      <c r="N18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="13" t="n"/>
@@ -2097,13 +1958,6 @@
       <c r="E19" s="13" t="n"/>
       <c r="F19" s="13" t="n"/>
       <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="13" t="n"/>
@@ -2112,13 +1966,6 @@
       <c r="E20" s="13" t="n"/>
       <c r="F20" s="13" t="n"/>
       <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="13" t="n"/>
@@ -2127,13 +1974,6 @@
       <c r="E21" s="13" t="n"/>
       <c r="F21" s="13" t="n"/>
       <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="13" t="n"/>
@@ -2142,13 +1982,6 @@
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="13" t="n"/>
       <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="13" t="n"/>
-      <c r="M22" s="13" t="n"/>
-      <c r="N22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="13" t="n"/>
@@ -2157,13 +1990,6 @@
       <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="n"/>
       <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="13" t="n"/>
-      <c r="N23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="13" t="n"/>
@@ -2172,13 +1998,6 @@
       <c r="E24" s="13" t="n"/>
       <c r="F24" s="13" t="n"/>
       <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="13" t="n"/>
@@ -2187,13 +2006,6 @@
       <c r="E25" s="13" t="n"/>
       <c r="F25" s="13" t="n"/>
       <c r="G25" s="13" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="13" t="n"/>
-      <c r="N25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="13" t="n"/>
@@ -2202,13 +2014,6 @@
       <c r="E26" s="13" t="n"/>
       <c r="F26" s="13" t="n"/>
       <c r="G26" s="13" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="13" t="n"/>
@@ -2217,13 +2022,6 @@
       <c r="E27" s="13" t="n"/>
       <c r="F27" s="13" t="n"/>
       <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="13" t="n"/>
-      <c r="N27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="13" t="n"/>
@@ -2232,13 +2030,6 @@
       <c r="E28" s="13" t="n"/>
       <c r="F28" s="13" t="n"/>
       <c r="G28" s="13" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="13" t="n"/>
@@ -2247,13 +2038,6 @@
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
       <c r="G29" s="13" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="13" t="n"/>
-      <c r="N29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="13" t="n"/>
@@ -2262,13 +2046,6 @@
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
       <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="13" t="n"/>
-      <c r="N30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="13" t="n"/>
@@ -2277,13 +2054,6 @@
       <c r="E31" s="13" t="n"/>
       <c r="F31" s="13" t="n"/>
       <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="13" t="n"/>
-      <c r="N31" s="13" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="13" t="n"/>
@@ -2292,13 +2062,6 @@
       <c r="E32" s="13" t="n"/>
       <c r="F32" s="13" t="n"/>
       <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="13" t="n"/>
-      <c r="N32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="13" t="n"/>
@@ -2307,13 +2070,6 @@
       <c r="E33" s="13" t="n"/>
       <c r="F33" s="13" t="n"/>
       <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="13" t="n"/>
-      <c r="N33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="13" t="n"/>
@@ -2322,13 +2078,6 @@
       <c r="E34" s="13" t="n"/>
       <c r="F34" s="13" t="n"/>
       <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="13" t="n"/>
@@ -2337,13 +2086,6 @@
       <c r="E35" s="13" t="n"/>
       <c r="F35" s="13" t="n"/>
       <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="13" t="n"/>
-      <c r="N35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="13" t="n"/>
@@ -2352,13 +2094,6 @@
       <c r="E36" s="13" t="n"/>
       <c r="F36" s="13" t="n"/>
       <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
-      <c r="L36" s="13" t="n"/>
-      <c r="M36" s="13" t="n"/>
-      <c r="N36" s="13" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="13" t="n"/>
@@ -2367,13 +2102,6 @@
       <c r="E37" s="13" t="n"/>
       <c r="F37" s="13" t="n"/>
       <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="13" t="n"/>
-      <c r="N37" s="13" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="13" t="n"/>
@@ -2382,13 +2110,6 @@
       <c r="E38" s="13" t="n"/>
       <c r="F38" s="13" t="n"/>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="13" t="n"/>
-      <c r="N38" s="13" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="13" t="n"/>
@@ -2397,13 +2118,6 @@
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="13" t="n"/>
       <c r="G39" s="13" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="13" t="n"/>
-      <c r="L39" s="13" t="n"/>
-      <c r="M39" s="13" t="n"/>
-      <c r="N39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="13" t="n"/>
@@ -2412,13 +2126,6 @@
       <c r="E40" s="13" t="n"/>
       <c r="F40" s="13" t="n"/>
       <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="13" t="n"/>
-      <c r="L40" s="13" t="n"/>
-      <c r="M40" s="13" t="n"/>
-      <c r="N40" s="13" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="13" t="n"/>
@@ -2427,13 +2134,6 @@
       <c r="E41" s="13" t="n"/>
       <c r="F41" s="13" t="n"/>
       <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
-      <c r="L41" s="13" t="n"/>
-      <c r="M41" s="13" t="n"/>
-      <c r="N41" s="13" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="13" t="n"/>
@@ -2442,13 +2142,6 @@
       <c r="E42" s="13" t="n"/>
       <c r="F42" s="13" t="n"/>
       <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="n"/>
-      <c r="M42" s="13" t="n"/>
-      <c r="N42" s="13" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="13" t="n"/>
@@ -2457,13 +2150,6 @@
       <c r="E43" s="13" t="n"/>
       <c r="F43" s="13" t="n"/>
       <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-      <c r="I43" s="13" t="n"/>
-      <c r="J43" s="13" t="n"/>
-      <c r="K43" s="13" t="n"/>
-      <c r="L43" s="13" t="n"/>
-      <c r="M43" s="13" t="n"/>
-      <c r="N43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="13" t="n"/>
@@ -2472,13 +2158,6 @@
       <c r="E44" s="13" t="n"/>
       <c r="F44" s="13" t="n"/>
       <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="13" t="n"/>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="13" t="n"/>
-      <c r="N44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="13" t="n"/>
@@ -2487,13 +2166,6 @@
       <c r="E45" s="13" t="n"/>
       <c r="F45" s="13" t="n"/>
       <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="13" t="n"/>
-      <c r="N45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="13" t="n"/>
@@ -2502,13 +2174,6 @@
       <c r="E46" s="13" t="n"/>
       <c r="F46" s="13" t="n"/>
       <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
-      <c r="J46" s="13" t="n"/>
-      <c r="K46" s="13" t="n"/>
-      <c r="L46" s="13" t="n"/>
-      <c r="M46" s="13" t="n"/>
-      <c r="N46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="13" t="n"/>
@@ -2517,13 +2182,6 @@
       <c r="E47" s="13" t="n"/>
       <c r="F47" s="13" t="n"/>
       <c r="G47" s="13" t="n"/>
-      <c r="H47" s="13" t="n"/>
-      <c r="I47" s="13" t="n"/>
-      <c r="J47" s="13" t="n"/>
-      <c r="K47" s="13" t="n"/>
-      <c r="L47" s="13" t="n"/>
-      <c r="M47" s="13" t="n"/>
-      <c r="N47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="13" t="n"/>
@@ -2532,13 +2190,6 @@
       <c r="E48" s="13" t="n"/>
       <c r="F48" s="13" t="n"/>
       <c r="G48" s="13" t="n"/>
-      <c r="H48" s="13" t="n"/>
-      <c r="I48" s="13" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="K48" s="13" t="n"/>
-      <c r="L48" s="13" t="n"/>
-      <c r="M48" s="13" t="n"/>
-      <c r="N48" s="13" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="13" t="n"/>
@@ -2547,13 +2198,6 @@
       <c r="E49" s="13" t="n"/>
       <c r="F49" s="13" t="n"/>
       <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-      <c r="I49" s="13" t="n"/>
-      <c r="J49" s="13" t="n"/>
-      <c r="K49" s="13" t="n"/>
-      <c r="L49" s="13" t="n"/>
-      <c r="M49" s="13" t="n"/>
-      <c r="N49" s="13" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="13" t="n"/>
@@ -2562,13 +2206,6 @@
       <c r="E50" s="13" t="n"/>
       <c r="F50" s="13" t="n"/>
       <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="13" t="n"/>
-      <c r="J50" s="13" t="n"/>
-      <c r="K50" s="13" t="n"/>
-      <c r="L50" s="13" t="n"/>
-      <c r="M50" s="13" t="n"/>
-      <c r="N50" s="13" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="13" t="n"/>
@@ -2577,13 +2214,6 @@
       <c r="E51" s="13" t="n"/>
       <c r="F51" s="13" t="n"/>
       <c r="G51" s="13" t="n"/>
-      <c r="H51" s="13" t="n"/>
-      <c r="I51" s="13" t="n"/>
-      <c r="J51" s="13" t="n"/>
-      <c r="K51" s="13" t="n"/>
-      <c r="L51" s="13" t="n"/>
-      <c r="M51" s="13" t="n"/>
-      <c r="N51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="13" t="n"/>
@@ -2592,13 +2222,6 @@
       <c r="E52" s="13" t="n"/>
       <c r="F52" s="13" t="n"/>
       <c r="G52" s="13" t="n"/>
-      <c r="H52" s="13" t="n"/>
-      <c r="I52" s="13" t="n"/>
-      <c r="J52" s="13" t="n"/>
-      <c r="K52" s="13" t="n"/>
-      <c r="L52" s="13" t="n"/>
-      <c r="M52" s="13" t="n"/>
-      <c r="N52" s="13" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="13" t="n"/>
@@ -2607,13 +2230,6 @@
       <c r="E53" s="13" t="n"/>
       <c r="F53" s="13" t="n"/>
       <c r="G53" s="13" t="n"/>
-      <c r="H53" s="13" t="n"/>
-      <c r="I53" s="13" t="n"/>
-      <c r="J53" s="13" t="n"/>
-      <c r="K53" s="13" t="n"/>
-      <c r="L53" s="13" t="n"/>
-      <c r="M53" s="13" t="n"/>
-      <c r="N53" s="13" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="13" t="n"/>
@@ -2622,13 +2238,6 @@
       <c r="E54" s="13" t="n"/>
       <c r="F54" s="13" t="n"/>
       <c r="G54" s="13" t="n"/>
-      <c r="H54" s="13" t="n"/>
-      <c r="I54" s="13" t="n"/>
-      <c r="J54" s="13" t="n"/>
-      <c r="K54" s="13" t="n"/>
-      <c r="L54" s="13" t="n"/>
-      <c r="M54" s="13" t="n"/>
-      <c r="N54" s="13" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="13" t="n"/>
@@ -2637,13 +2246,6 @@
       <c r="E55" s="13" t="n"/>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="13" t="n"/>
-      <c r="H55" s="13" t="n"/>
-      <c r="I55" s="13" t="n"/>
-      <c r="J55" s="13" t="n"/>
-      <c r="K55" s="13" t="n"/>
-      <c r="L55" s="13" t="n"/>
-      <c r="M55" s="13" t="n"/>
-      <c r="N55" s="13" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="13" t="n"/>
@@ -2652,13 +2254,6 @@
       <c r="E56" s="13" t="n"/>
       <c r="F56" s="13" t="n"/>
       <c r="G56" s="13" t="n"/>
-      <c r="H56" s="13" t="n"/>
-      <c r="I56" s="13" t="n"/>
-      <c r="J56" s="13" t="n"/>
-      <c r="K56" s="13" t="n"/>
-      <c r="L56" s="13" t="n"/>
-      <c r="M56" s="13" t="n"/>
-      <c r="N56" s="13" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="13" t="n"/>
@@ -2667,13 +2262,6 @@
       <c r="E57" s="13" t="n"/>
       <c r="F57" s="13" t="n"/>
       <c r="G57" s="13" t="n"/>
-      <c r="H57" s="13" t="n"/>
-      <c r="I57" s="13" t="n"/>
-      <c r="J57" s="13" t="n"/>
-      <c r="K57" s="13" t="n"/>
-      <c r="L57" s="13" t="n"/>
-      <c r="M57" s="13" t="n"/>
-      <c r="N57" s="13" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="13" t="n"/>
@@ -2682,13 +2270,6 @@
       <c r="E58" s="13" t="n"/>
       <c r="F58" s="13" t="n"/>
       <c r="G58" s="13" t="n"/>
-      <c r="H58" s="13" t="n"/>
-      <c r="I58" s="13" t="n"/>
-      <c r="J58" s="13" t="n"/>
-      <c r="K58" s="13" t="n"/>
-      <c r="L58" s="13" t="n"/>
-      <c r="M58" s="13" t="n"/>
-      <c r="N58" s="13" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="13" t="n"/>
@@ -2697,13 +2278,6 @@
       <c r="E59" s="13" t="n"/>
       <c r="F59" s="13" t="n"/>
       <c r="G59" s="13" t="n"/>
-      <c r="H59" s="13" t="n"/>
-      <c r="I59" s="13" t="n"/>
-      <c r="J59" s="13" t="n"/>
-      <c r="K59" s="13" t="n"/>
-      <c r="L59" s="13" t="n"/>
-      <c r="M59" s="13" t="n"/>
-      <c r="N59" s="13" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="13" t="n"/>
@@ -2712,13 +2286,6 @@
       <c r="E60" s="13" t="n"/>
       <c r="F60" s="13" t="n"/>
       <c r="G60" s="13" t="n"/>
-      <c r="H60" s="13" t="n"/>
-      <c r="I60" s="13" t="n"/>
-      <c r="J60" s="13" t="n"/>
-      <c r="K60" s="13" t="n"/>
-      <c r="L60" s="13" t="n"/>
-      <c r="M60" s="13" t="n"/>
-      <c r="N60" s="13" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="13" t="n"/>
@@ -2727,13 +2294,6 @@
       <c r="E61" s="13" t="n"/>
       <c r="F61" s="13" t="n"/>
       <c r="G61" s="13" t="n"/>
-      <c r="H61" s="13" t="n"/>
-      <c r="I61" s="13" t="n"/>
-      <c r="J61" s="13" t="n"/>
-      <c r="K61" s="13" t="n"/>
-      <c r="L61" s="13" t="n"/>
-      <c r="M61" s="13" t="n"/>
-      <c r="N61" s="13" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="13" t="n"/>
@@ -2742,13 +2302,6 @@
       <c r="E62" s="13" t="n"/>
       <c r="F62" s="13" t="n"/>
       <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
-      <c r="I62" s="13" t="n"/>
-      <c r="J62" s="13" t="n"/>
-      <c r="K62" s="13" t="n"/>
-      <c r="L62" s="13" t="n"/>
-      <c r="M62" s="13" t="n"/>
-      <c r="N62" s="13" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="13" t="n"/>
@@ -2757,13 +2310,6 @@
       <c r="E63" s="13" t="n"/>
       <c r="F63" s="13" t="n"/>
       <c r="G63" s="13" t="n"/>
-      <c r="H63" s="13" t="n"/>
-      <c r="I63" s="13" t="n"/>
-      <c r="J63" s="13" t="n"/>
-      <c r="K63" s="13" t="n"/>
-      <c r="L63" s="13" t="n"/>
-      <c r="M63" s="13" t="n"/>
-      <c r="N63" s="13" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="13" t="n"/>
@@ -2772,13 +2318,6 @@
       <c r="E64" s="13" t="n"/>
       <c r="F64" s="13" t="n"/>
       <c r="G64" s="13" t="n"/>
-      <c r="H64" s="13" t="n"/>
-      <c r="I64" s="13" t="n"/>
-      <c r="J64" s="13" t="n"/>
-      <c r="K64" s="13" t="n"/>
-      <c r="L64" s="13" t="n"/>
-      <c r="M64" s="13" t="n"/>
-      <c r="N64" s="13" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="13" t="n"/>
@@ -2787,13 +2326,6 @@
       <c r="E65" s="13" t="n"/>
       <c r="F65" s="13" t="n"/>
       <c r="G65" s="13" t="n"/>
-      <c r="H65" s="13" t="n"/>
-      <c r="I65" s="13" t="n"/>
-      <c r="J65" s="13" t="n"/>
-      <c r="K65" s="13" t="n"/>
-      <c r="L65" s="13" t="n"/>
-      <c r="M65" s="13" t="n"/>
-      <c r="N65" s="13" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="13" t="n"/>
@@ -2802,13 +2334,6 @@
       <c r="E66" s="13" t="n"/>
       <c r="F66" s="13" t="n"/>
       <c r="G66" s="13" t="n"/>
-      <c r="H66" s="13" t="n"/>
-      <c r="I66" s="13" t="n"/>
-      <c r="J66" s="13" t="n"/>
-      <c r="K66" s="13" t="n"/>
-      <c r="L66" s="13" t="n"/>
-      <c r="M66" s="13" t="n"/>
-      <c r="N66" s="13" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="13" t="n"/>
@@ -2817,13 +2342,6 @@
       <c r="E67" s="13" t="n"/>
       <c r="F67" s="13" t="n"/>
       <c r="G67" s="13" t="n"/>
-      <c r="H67" s="13" t="n"/>
-      <c r="I67" s="13" t="n"/>
-      <c r="J67" s="13" t="n"/>
-      <c r="K67" s="13" t="n"/>
-      <c r="L67" s="13" t="n"/>
-      <c r="M67" s="13" t="n"/>
-      <c r="N67" s="13" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="13" t="n"/>
@@ -2832,13 +2350,6 @@
       <c r="E68" s="13" t="n"/>
       <c r="F68" s="13" t="n"/>
       <c r="G68" s="13" t="n"/>
-      <c r="H68" s="13" t="n"/>
-      <c r="I68" s="13" t="n"/>
-      <c r="J68" s="13" t="n"/>
-      <c r="K68" s="13" t="n"/>
-      <c r="L68" s="13" t="n"/>
-      <c r="M68" s="13" t="n"/>
-      <c r="N68" s="13" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="13" t="n"/>
@@ -2847,13 +2358,6 @@
       <c r="E69" s="13" t="n"/>
       <c r="F69" s="13" t="n"/>
       <c r="G69" s="13" t="n"/>
-      <c r="H69" s="13" t="n"/>
-      <c r="I69" s="13" t="n"/>
-      <c r="J69" s="13" t="n"/>
-      <c r="K69" s="13" t="n"/>
-      <c r="L69" s="13" t="n"/>
-      <c r="M69" s="13" t="n"/>
-      <c r="N69" s="13" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="13" t="n"/>
@@ -2862,13 +2366,6 @@
       <c r="E70" s="13" t="n"/>
       <c r="F70" s="13" t="n"/>
       <c r="G70" s="13" t="n"/>
-      <c r="H70" s="13" t="n"/>
-      <c r="I70" s="13" t="n"/>
-      <c r="J70" s="13" t="n"/>
-      <c r="K70" s="13" t="n"/>
-      <c r="L70" s="13" t="n"/>
-      <c r="M70" s="13" t="n"/>
-      <c r="N70" s="13" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="13" t="n"/>
@@ -2877,13 +2374,6 @@
       <c r="E71" s="13" t="n"/>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="13" t="n"/>
-      <c r="H71" s="13" t="n"/>
-      <c r="I71" s="13" t="n"/>
-      <c r="J71" s="13" t="n"/>
-      <c r="K71" s="13" t="n"/>
-      <c r="L71" s="13" t="n"/>
-      <c r="M71" s="13" t="n"/>
-      <c r="N71" s="13" t="n"/>
     </row>
     <row r="72">
       <c r="B72" s="13" t="n"/>
@@ -2892,13 +2382,6 @@
       <c r="E72" s="13" t="n"/>
       <c r="F72" s="13" t="n"/>
       <c r="G72" s="13" t="n"/>
-      <c r="H72" s="13" t="n"/>
-      <c r="I72" s="13" t="n"/>
-      <c r="J72" s="13" t="n"/>
-      <c r="K72" s="13" t="n"/>
-      <c r="L72" s="13" t="n"/>
-      <c r="M72" s="13" t="n"/>
-      <c r="N72" s="13" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="13" t="n"/>
@@ -2907,13 +2390,6 @@
       <c r="E73" s="13" t="n"/>
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="13" t="n"/>
-      <c r="H73" s="13" t="n"/>
-      <c r="I73" s="13" t="n"/>
-      <c r="J73" s="13" t="n"/>
-      <c r="K73" s="13" t="n"/>
-      <c r="L73" s="13" t="n"/>
-      <c r="M73" s="13" t="n"/>
-      <c r="N73" s="13" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="13" t="n"/>
@@ -2922,13 +2398,6 @@
       <c r="E74" s="13" t="n"/>
       <c r="F74" s="13" t="n"/>
       <c r="G74" s="13" t="n"/>
-      <c r="H74" s="13" t="n"/>
-      <c r="I74" s="13" t="n"/>
-      <c r="J74" s="13" t="n"/>
-      <c r="K74" s="13" t="n"/>
-      <c r="L74" s="13" t="n"/>
-      <c r="M74" s="13" t="n"/>
-      <c r="N74" s="13" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="13" t="n"/>
@@ -2937,13 +2406,6 @@
       <c r="E75" s="13" t="n"/>
       <c r="F75" s="13" t="n"/>
       <c r="G75" s="13" t="n"/>
-      <c r="H75" s="13" t="n"/>
-      <c r="I75" s="13" t="n"/>
-      <c r="J75" s="13" t="n"/>
-      <c r="K75" s="13" t="n"/>
-      <c r="L75" s="13" t="n"/>
-      <c r="M75" s="13" t="n"/>
-      <c r="N75" s="13" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="13" t="n"/>
@@ -2952,13 +2414,6 @@
       <c r="E76" s="13" t="n"/>
       <c r="F76" s="13" t="n"/>
       <c r="G76" s="13" t="n"/>
-      <c r="H76" s="13" t="n"/>
-      <c r="I76" s="13" t="n"/>
-      <c r="J76" s="13" t="n"/>
-      <c r="K76" s="13" t="n"/>
-      <c r="L76" s="13" t="n"/>
-      <c r="M76" s="13" t="n"/>
-      <c r="N76" s="13" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="13" t="n"/>
@@ -2967,13 +2422,6 @@
       <c r="E77" s="13" t="n"/>
       <c r="F77" s="13" t="n"/>
       <c r="G77" s="13" t="n"/>
-      <c r="H77" s="13" t="n"/>
-      <c r="I77" s="13" t="n"/>
-      <c r="J77" s="13" t="n"/>
-      <c r="K77" s="13" t="n"/>
-      <c r="L77" s="13" t="n"/>
-      <c r="M77" s="13" t="n"/>
-      <c r="N77" s="13" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="13" t="n"/>
@@ -2982,13 +2430,6 @@
       <c r="E78" s="13" t="n"/>
       <c r="F78" s="13" t="n"/>
       <c r="G78" s="13" t="n"/>
-      <c r="H78" s="13" t="n"/>
-      <c r="I78" s="13" t="n"/>
-      <c r="J78" s="13" t="n"/>
-      <c r="K78" s="13" t="n"/>
-      <c r="L78" s="13" t="n"/>
-      <c r="M78" s="13" t="n"/>
-      <c r="N78" s="13" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="13" t="n"/>
@@ -2997,13 +2438,6 @@
       <c r="E79" s="13" t="n"/>
       <c r="F79" s="13" t="n"/>
       <c r="G79" s="13" t="n"/>
-      <c r="H79" s="13" t="n"/>
-      <c r="I79" s="13" t="n"/>
-      <c r="J79" s="13" t="n"/>
-      <c r="K79" s="13" t="n"/>
-      <c r="L79" s="13" t="n"/>
-      <c r="M79" s="13" t="n"/>
-      <c r="N79" s="13" t="n"/>
     </row>
     <row r="80">
       <c r="B80" s="13" t="n"/>
@@ -3012,13 +2446,6 @@
       <c r="E80" s="13" t="n"/>
       <c r="F80" s="13" t="n"/>
       <c r="G80" s="13" t="n"/>
-      <c r="H80" s="13" t="n"/>
-      <c r="I80" s="13" t="n"/>
-      <c r="J80" s="13" t="n"/>
-      <c r="K80" s="13" t="n"/>
-      <c r="L80" s="13" t="n"/>
-      <c r="M80" s="13" t="n"/>
-      <c r="N80" s="13" t="n"/>
     </row>
     <row r="81">
       <c r="B81" s="13" t="n"/>
@@ -3027,13 +2454,6 @@
       <c r="E81" s="13" t="n"/>
       <c r="F81" s="13" t="n"/>
       <c r="G81" s="13" t="n"/>
-      <c r="H81" s="13" t="n"/>
-      <c r="I81" s="13" t="n"/>
-      <c r="J81" s="13" t="n"/>
-      <c r="K81" s="13" t="n"/>
-      <c r="L81" s="13" t="n"/>
-      <c r="M81" s="13" t="n"/>
-      <c r="N81" s="13" t="n"/>
     </row>
     <row r="82">
       <c r="B82" s="13" t="n"/>
@@ -3042,13 +2462,6 @@
       <c r="E82" s="13" t="n"/>
       <c r="F82" s="13" t="n"/>
       <c r="G82" s="13" t="n"/>
-      <c r="H82" s="13" t="n"/>
-      <c r="I82" s="13" t="n"/>
-      <c r="J82" s="13" t="n"/>
-      <c r="K82" s="13" t="n"/>
-      <c r="L82" s="13" t="n"/>
-      <c r="M82" s="13" t="n"/>
-      <c r="N82" s="13" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="13" t="n"/>
@@ -3057,13 +2470,6 @@
       <c r="E83" s="13" t="n"/>
       <c r="F83" s="13" t="n"/>
       <c r="G83" s="13" t="n"/>
-      <c r="H83" s="13" t="n"/>
-      <c r="I83" s="13" t="n"/>
-      <c r="J83" s="13" t="n"/>
-      <c r="K83" s="13" t="n"/>
-      <c r="L83" s="13" t="n"/>
-      <c r="M83" s="13" t="n"/>
-      <c r="N83" s="13" t="n"/>
     </row>
     <row r="84">
       <c r="B84" s="13" t="n"/>
@@ -3072,13 +2478,6 @@
       <c r="E84" s="13" t="n"/>
       <c r="F84" s="13" t="n"/>
       <c r="G84" s="13" t="n"/>
-      <c r="H84" s="13" t="n"/>
-      <c r="I84" s="13" t="n"/>
-      <c r="J84" s="13" t="n"/>
-      <c r="K84" s="13" t="n"/>
-      <c r="L84" s="13" t="n"/>
-      <c r="M84" s="13" t="n"/>
-      <c r="N84" s="13" t="n"/>
     </row>
     <row r="85">
       <c r="B85" s="13" t="n"/>
@@ -3087,17 +2486,170 @@
       <c r="E85" s="13" t="n"/>
       <c r="F85" s="13" t="n"/>
       <c r="G85" s="13" t="n"/>
-      <c r="H85" s="13" t="n"/>
-      <c r="I85" s="13" t="n"/>
-      <c r="J85" s="13" t="n"/>
-      <c r="K85" s="13" t="n"/>
-      <c r="L85" s="13" t="n"/>
-      <c r="M85" s="13" t="n"/>
-      <c r="N85" s="13" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="13" t="n"/>
+      <c r="C86" s="13" t="n"/>
+      <c r="D86" s="13" t="n"/>
+      <c r="E86" s="13" t="n"/>
+      <c r="F86" s="13" t="n"/>
+      <c r="G86" s="13" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="13" t="n"/>
+      <c r="C87" s="13" t="n"/>
+      <c r="D87" s="13" t="n"/>
+      <c r="E87" s="13" t="n"/>
+      <c r="F87" s="13" t="n"/>
+      <c r="G87" s="13" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="13" t="n"/>
+      <c r="C88" s="13" t="n"/>
+      <c r="D88" s="13" t="n"/>
+      <c r="E88" s="13" t="n"/>
+      <c r="F88" s="13" t="n"/>
+      <c r="G88" s="13" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="13" t="n"/>
+      <c r="C89" s="13" t="n"/>
+      <c r="D89" s="13" t="n"/>
+      <c r="E89" s="13" t="n"/>
+      <c r="F89" s="13" t="n"/>
+      <c r="G89" s="13" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="13" t="n"/>
+      <c r="C90" s="13" t="n"/>
+      <c r="D90" s="13" t="n"/>
+      <c r="E90" s="13" t="n"/>
+      <c r="F90" s="13" t="n"/>
+      <c r="G90" s="13" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="13" t="n"/>
+      <c r="C91" s="13" t="n"/>
+      <c r="D91" s="13" t="n"/>
+      <c r="E91" s="13" t="n"/>
+      <c r="F91" s="13" t="n"/>
+      <c r="G91" s="13" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="13" t="n"/>
+      <c r="C92" s="13" t="n"/>
+      <c r="D92" s="13" t="n"/>
+      <c r="E92" s="13" t="n"/>
+      <c r="F92" s="13" t="n"/>
+      <c r="G92" s="13" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="13" t="n"/>
+      <c r="C93" s="13" t="n"/>
+      <c r="D93" s="13" t="n"/>
+      <c r="E93" s="13" t="n"/>
+      <c r="F93" s="13" t="n"/>
+      <c r="G93" s="13" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="13" t="n"/>
+      <c r="C94" s="13" t="n"/>
+      <c r="D94" s="13" t="n"/>
+      <c r="E94" s="13" t="n"/>
+      <c r="F94" s="13" t="n"/>
+      <c r="G94" s="13" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="13" t="n"/>
+      <c r="C95" s="13" t="n"/>
+      <c r="D95" s="13" t="n"/>
+      <c r="E95" s="13" t="n"/>
+      <c r="F95" s="13" t="n"/>
+      <c r="G95" s="13" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="13" t="n"/>
+      <c r="C96" s="13" t="n"/>
+      <c r="D96" s="13" t="n"/>
+      <c r="E96" s="13" t="n"/>
+      <c r="F96" s="13" t="n"/>
+      <c r="G96" s="13" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="13" t="n"/>
+      <c r="C97" s="13" t="n"/>
+      <c r="D97" s="13" t="n"/>
+      <c r="E97" s="13" t="n"/>
+      <c r="F97" s="13" t="n"/>
+      <c r="G97" s="13" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="13" t="n"/>
+      <c r="C98" s="13" t="n"/>
+      <c r="D98" s="13" t="n"/>
+      <c r="E98" s="13" t="n"/>
+      <c r="F98" s="13" t="n"/>
+      <c r="G98" s="13" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="13" t="n"/>
+      <c r="C99" s="13" t="n"/>
+      <c r="D99" s="13" t="n"/>
+      <c r="E99" s="13" t="n"/>
+      <c r="F99" s="13" t="n"/>
+      <c r="G99" s="13" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="13" t="n"/>
+      <c r="C100" s="13" t="n"/>
+      <c r="D100" s="13" t="n"/>
+      <c r="E100" s="13" t="n"/>
+      <c r="F100" s="13" t="n"/>
+      <c r="G100" s="13" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="13" t="n"/>
+      <c r="C101" s="13" t="n"/>
+      <c r="D101" s="13" t="n"/>
+      <c r="E101" s="13" t="n"/>
+      <c r="F101" s="13" t="n"/>
+      <c r="G101" s="13" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="13" t="n"/>
+      <c r="C102" s="13" t="n"/>
+      <c r="D102" s="13" t="n"/>
+      <c r="E102" s="13" t="n"/>
+      <c r="F102" s="13" t="n"/>
+      <c r="G102" s="13" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="13" t="n"/>
+      <c r="C103" s="13" t="n"/>
+      <c r="D103" s="13" t="n"/>
+      <c r="E103" s="13" t="n"/>
+      <c r="F103" s="13" t="n"/>
+      <c r="G103" s="13" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="13" t="n"/>
+      <c r="C104" s="13" t="n"/>
+      <c r="D104" s="13" t="n"/>
+      <c r="E104" s="13" t="n"/>
+      <c r="F104" s="13" t="n"/>
+      <c r="G104" s="13" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="13" t="n"/>
+      <c r="C105" s="13" t="n"/>
+      <c r="D105" s="13" t="n"/>
+      <c r="E105" s="13" t="n"/>
+      <c r="F105" s="13" t="n"/>
+      <c r="G105" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3109,7 +2661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:T21"/>
+  <dimension ref="B2:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3125,13 +2677,14 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -3144,102 +2697,107 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ ⑤実証結果集計は、この表の5〜19行目を参照しています。行の挿入は19行目より上で行ってください。</t>
+          <t>※ ⑤実証結果集計はこの表の5〜19行目を参照しています。行の挿入は19行目より上で行ってください。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>参加者</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>陣</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>達成/未達</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>初売上までの日数</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>総作業時間(h)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>売上金額</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>購入者数</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>開始時フォロワー</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>本業形態</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>1日の確保時間</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>文章経験</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>AI生成割合</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>手直しの程度</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>負荷感</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>最もつまずいた工程</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>推奨度(0-10)</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>公開可否</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>公開名義</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>体験談</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>補助:達成者の日数</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>補助:達成者の作業時間</t>
         </is>
@@ -3263,11 +2821,12 @@
       <c r="P5" s="14" t="n"/>
       <c r="Q5" s="14" t="n"/>
       <c r="R5" s="14" t="n"/>
-      <c r="S5" s="7">
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="8">
         <f>IF($D5="達成",$E5,"")</f>
         <v/>
       </c>
-      <c r="T5" s="7">
+      <c r="U5" s="8">
         <f>IF($D5="達成",$F5,"")</f>
         <v/>
       </c>
@@ -3290,11 +2849,12 @@
       <c r="P6" s="14" t="n"/>
       <c r="Q6" s="14" t="n"/>
       <c r="R6" s="14" t="n"/>
-      <c r="S6" s="7">
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="8">
         <f>IF($D6="達成",$E6,"")</f>
         <v/>
       </c>
-      <c r="T6" s="7">
+      <c r="U6" s="8">
         <f>IF($D6="達成",$F6,"")</f>
         <v/>
       </c>
@@ -3317,11 +2877,12 @@
       <c r="P7" s="14" t="n"/>
       <c r="Q7" s="14" t="n"/>
       <c r="R7" s="14" t="n"/>
-      <c r="S7" s="7">
+      <c r="S7" s="14" t="n"/>
+      <c r="T7" s="8">
         <f>IF($D7="達成",$E7,"")</f>
         <v/>
       </c>
-      <c r="T7" s="7">
+      <c r="U7" s="8">
         <f>IF($D7="達成",$F7,"")</f>
         <v/>
       </c>
@@ -3344,11 +2905,12 @@
       <c r="P8" s="14" t="n"/>
       <c r="Q8" s="14" t="n"/>
       <c r="R8" s="14" t="n"/>
-      <c r="S8" s="7">
+      <c r="S8" s="14" t="n"/>
+      <c r="T8" s="8">
         <f>IF($D8="達成",$E8,"")</f>
         <v/>
       </c>
-      <c r="T8" s="7">
+      <c r="U8" s="8">
         <f>IF($D8="達成",$F8,"")</f>
         <v/>
       </c>
@@ -3371,11 +2933,12 @@
       <c r="P9" s="14" t="n"/>
       <c r="Q9" s="14" t="n"/>
       <c r="R9" s="14" t="n"/>
-      <c r="S9" s="7">
+      <c r="S9" s="14" t="n"/>
+      <c r="T9" s="8">
         <f>IF($D9="達成",$E9,"")</f>
         <v/>
       </c>
-      <c r="T9" s="7">
+      <c r="U9" s="8">
         <f>IF($D9="達成",$F9,"")</f>
         <v/>
       </c>
@@ -3398,11 +2961,12 @@
       <c r="P10" s="14" t="n"/>
       <c r="Q10" s="14" t="n"/>
       <c r="R10" s="14" t="n"/>
-      <c r="S10" s="7">
+      <c r="S10" s="14" t="n"/>
+      <c r="T10" s="8">
         <f>IF($D10="達成",$E10,"")</f>
         <v/>
       </c>
-      <c r="T10" s="7">
+      <c r="U10" s="8">
         <f>IF($D10="達成",$F10,"")</f>
         <v/>
       </c>
@@ -3425,11 +2989,12 @@
       <c r="P11" s="14" t="n"/>
       <c r="Q11" s="14" t="n"/>
       <c r="R11" s="14" t="n"/>
-      <c r="S11" s="7">
+      <c r="S11" s="14" t="n"/>
+      <c r="T11" s="8">
         <f>IF($D11="達成",$E11,"")</f>
         <v/>
       </c>
-      <c r="T11" s="7">
+      <c r="U11" s="8">
         <f>IF($D11="達成",$F11,"")</f>
         <v/>
       </c>
@@ -3452,11 +3017,12 @@
       <c r="P12" s="14" t="n"/>
       <c r="Q12" s="14" t="n"/>
       <c r="R12" s="14" t="n"/>
-      <c r="S12" s="7">
+      <c r="S12" s="14" t="n"/>
+      <c r="T12" s="8">
         <f>IF($D12="達成",$E12,"")</f>
         <v/>
       </c>
-      <c r="T12" s="7">
+      <c r="U12" s="8">
         <f>IF($D12="達成",$F12,"")</f>
         <v/>
       </c>
@@ -3479,11 +3045,12 @@
       <c r="P13" s="14" t="n"/>
       <c r="Q13" s="14" t="n"/>
       <c r="R13" s="14" t="n"/>
-      <c r="S13" s="7">
+      <c r="S13" s="14" t="n"/>
+      <c r="T13" s="8">
         <f>IF($D13="達成",$E13,"")</f>
         <v/>
       </c>
-      <c r="T13" s="7">
+      <c r="U13" s="8">
         <f>IF($D13="達成",$F13,"")</f>
         <v/>
       </c>
@@ -3506,11 +3073,12 @@
       <c r="P14" s="14" t="n"/>
       <c r="Q14" s="14" t="n"/>
       <c r="R14" s="14" t="n"/>
-      <c r="S14" s="7">
+      <c r="S14" s="14" t="n"/>
+      <c r="T14" s="8">
         <f>IF($D14="達成",$E14,"")</f>
         <v/>
       </c>
-      <c r="T14" s="7">
+      <c r="U14" s="8">
         <f>IF($D14="達成",$F14,"")</f>
         <v/>
       </c>
@@ -3533,11 +3101,12 @@
       <c r="P15" s="14" t="n"/>
       <c r="Q15" s="14" t="n"/>
       <c r="R15" s="14" t="n"/>
-      <c r="S15" s="7">
+      <c r="S15" s="14" t="n"/>
+      <c r="T15" s="8">
         <f>IF($D15="達成",$E15,"")</f>
         <v/>
       </c>
-      <c r="T15" s="7">
+      <c r="U15" s="8">
         <f>IF($D15="達成",$F15,"")</f>
         <v/>
       </c>
@@ -3560,11 +3129,12 @@
       <c r="P16" s="14" t="n"/>
       <c r="Q16" s="14" t="n"/>
       <c r="R16" s="14" t="n"/>
-      <c r="S16" s="7">
+      <c r="S16" s="14" t="n"/>
+      <c r="T16" s="8">
         <f>IF($D16="達成",$E16,"")</f>
         <v/>
       </c>
-      <c r="T16" s="7">
+      <c r="U16" s="8">
         <f>IF($D16="達成",$F16,"")</f>
         <v/>
       </c>
@@ -3587,11 +3157,12 @@
       <c r="P17" s="14" t="n"/>
       <c r="Q17" s="14" t="n"/>
       <c r="R17" s="14" t="n"/>
-      <c r="S17" s="7">
+      <c r="S17" s="14" t="n"/>
+      <c r="T17" s="8">
         <f>IF($D17="達成",$E17,"")</f>
         <v/>
       </c>
-      <c r="T17" s="7">
+      <c r="U17" s="8">
         <f>IF($D17="達成",$F17,"")</f>
         <v/>
       </c>
@@ -3614,11 +3185,12 @@
       <c r="P18" s="14" t="n"/>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14" t="n"/>
-      <c r="S18" s="7">
+      <c r="S18" s="14" t="n"/>
+      <c r="T18" s="8">
         <f>IF($D18="達成",$E18,"")</f>
         <v/>
       </c>
-      <c r="T18" s="7">
+      <c r="U18" s="8">
         <f>IF($D18="達成",$F18,"")</f>
         <v/>
       </c>
@@ -3641,11 +3213,12 @@
       <c r="P19" s="14" t="n"/>
       <c r="Q19" s="14" t="n"/>
       <c r="R19" s="14" t="n"/>
-      <c r="S19" s="7">
+      <c r="S19" s="14" t="n"/>
+      <c r="T19" s="8">
         <f>IF($D19="達成",$E19,"")</f>
         <v/>
       </c>
-      <c r="T19" s="7">
+      <c r="U19" s="8">
         <f>IF($D19="達成",$F19,"")</f>
         <v/>
       </c>
@@ -3656,15 +3229,15 @@
           <t>凡例：黄色セルが入力欄です。「陣」は「第1陣」「第2陣」、「達成/未達」は「達成」「未達」と入力してください（⑤の集計がこの表記を参照しています）。</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>補助列S・Tは⑤実証結果集計の最短/最長の算出に使用します。手入力しないでください。</t>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>補助列は自動計算です。手入力しないでください。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="B2:S2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3676,7 +3249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D30"/>
+  <dimension ref="B2:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3685,7 +3258,6 @@
     <col width="58" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -3696,11 +3268,10 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ 数値は④完了サマリから自動計算されます。データ未入力の間は「-」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>※ ④完了サマリから自動計算されます。データ未入力の間は「-」と表示されます。</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -3709,52 +3280,52 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>参加者数（除外者を除く）</t>
         </is>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>COUNTA('④完了サマリ'!B5:B19)</f>
         <v/>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>④に記録された人数</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>達成者数</t>
         </is>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>COUNTIF('④完了サマリ'!D5:D19,"達成")</f>
         <v/>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>達成率</t>
         </is>
@@ -3763,14 +3334,14 @@
         <f>IF($C$7=0,"-",$C$8/$C$7)</f>
         <v/>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>運営提示時の中心指標</t>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>モニターは改善の場のため、この数字単体では評価しない</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>平均 初売上までの日数</t>
         </is>
@@ -3779,38 +3350,38 @@
         <f>IF($C$8=0,"-",AVERAGEIFS('④完了サマリ'!E5:E19,'④完了サマリ'!D5:D19,"達成"))</f>
         <v/>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>達成者のみで算出</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>達成者のみ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>最短 初売上までの日数</t>
         </is>
       </c>
       <c r="C11" s="16">
-        <f>IF($C$8=0,"-",MIN('④完了サマリ'!S5:S19))</f>
-        <v/>
-      </c>
-      <c r="D11" s="6" t="inlineStr"/>
+        <f>IF($C$8=0,"-",MIN('④完了サマリ'!T5:T19))</f>
+        <v/>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>最長 初売上までの日数</t>
         </is>
       </c>
       <c r="C12" s="16">
-        <f>IF($C$8=0,"-",MAX('④完了サマリ'!S5:S19))</f>
-        <v/>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
+        <f>IF($C$8=0,"-",MAX('④完了サマリ'!T5:T19))</f>
+        <v/>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>平均 総作業時間（時間）</t>
         </is>
@@ -3819,37 +3390,36 @@
         <f>IF($C$8=0,"-",AVERAGEIFS('④完了サマリ'!F5:F19,'④完了サマリ'!D5:D19,"達成"))</f>
         <v/>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>★ 差別化の中核指標</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>最短 総作業時間（時間）</t>
         </is>
       </c>
       <c r="C14" s="16">
-        <f>IF($C$8=0,"-",MIN('④完了サマリ'!T5:T19))</f>
-        <v/>
-      </c>
-      <c r="D14" s="6" t="inlineStr"/>
+        <f>IF($C$8=0,"-",MIN('④完了サマリ'!U5:U19))</f>
+        <v/>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>平均 推奨度（0-10）</t>
         </is>
       </c>
       <c r="C15" s="16">
-        <f>IF($C$8=0,"-",AVERAGEIFS('④完了サマリ'!P5:P19,'④完了サマリ'!D5:D19,"達成"))</f>
-        <v/>
-      </c>
-      <c r="D15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16"/>
+        <f>IF($C$8=0,"-",AVERAGEIFS('④完了サマリ'!Q5:Q19,'④完了サマリ'!D5:D19,"達成"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -3858,80 +3428,80 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>第1陣 参加者数</t>
         </is>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <f>COUNTIF('④完了サマリ'!C5:C19,"第1陣")</f>
         <v/>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>検証目的。達成率は実証数字に含めない</t>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>穴出しが目的。達成率は実証数字に含めない</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>第1陣 達成者数</t>
         </is>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <f>COUNTIFS('④完了サマリ'!C5:C19,"第1陣",'④完了サマリ'!D5:D19,"達成")</f>
         <v/>
       </c>
-      <c r="D20" s="6" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>第2陣 参加者数</t>
         </is>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <f>COUNTIF('④完了サマリ'!C5:C19,"第2陣")</f>
         <v/>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>改善後の本番</t>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>改善後</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>第2陣 達成者数</t>
         </is>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <f>COUNTIFS('④完了サマリ'!C5:C19,"第2陣",'④完了サマリ'!D5:D19,"達成")</f>
         <v/>
       </c>
-      <c r="D22" s="6" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>第2陣 達成率</t>
         </is>
@@ -3940,66 +3510,132 @@
         <f>IF(COUNTIFS('④完了サマリ'!C5:C19,"第2陣")=0,"-",COUNTIFS('④完了サマリ'!C5:C19,"第2陣",'④完了サマリ'!D5:D19,"達成")/COUNTIFS('④完了サマリ'!C5:C19,"第2陣"))</f>
         <v/>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>★ 運営に提示する数字はこれ</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>運営提示用サマリ（実証完了後に手書きで清書する）</t>
+          <t>改善サイクル（PDCA）の記録</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>例）フォロワー0の新規アカウントから、7名中◯名が◯日以内にnoteで初売上を達成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>第1陣で判明した詰まり</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>手順・ツール・レクチャーへの反映内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>運営提示用サマリ（実証完了後に清書する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>例）フォロワー0の新規アカウントから、第2陣7名中◯名が◯日以内にnoteで初売上を達成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　　平均総作業時間は◯時間。うち◯名はフルタイム勤務・文章未経験。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　文章の◯割はAIが生成し、手直しは「少し直した」以下が◯名。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>※ 上の数字は集計結果を転記して使用します。検証されていない数値を売り文句にしないこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="12" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　第1陣で判明した詰まり◯件をレクチャーと手順書に反映した上での結果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>※ 集計結果を転記して使用すること。検証されていない数値を売り文句にしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">　（Step4-3「誇大な表現で煽って売る人、根拠のない約束をする人」に自分が該当しないため）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B28:D28"/>
+  <mergeCells count="10">
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B39:D39"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
